--- a/tests/sam_tools/fixtures/simple_mip.xlsx
+++ b/tests/sam_tools/fixtures/simple_mip.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
@@ -470,16 +470,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -489,25 +489,25 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="n">
         <v>30</v>
       </c>
-      <c r="C3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D3" t="n">
-        <v>25</v>
-      </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -520,22 +520,22 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
         <v>20</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
